--- a/Template-UserStories-V2-1(1).xlsx
+++ b/Template-UserStories-V2-1(1).xlsx
@@ -506,6 +506,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Given</t>
     </r>
@@ -515,6 +516,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> I'm a Developer, 
 </t>
@@ -526,6 +528,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">When</t>
     </r>
@@ -535,6 +538,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve"> the system detects that the file is missing or corrupted,
 </t>
@@ -546,6 +550,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Then </t>
     </r>
@@ -555,6 +560,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">it displays a descriptive error message, prompts me to re-upload or skip, and logs the error details for reference.</t>
     </r>
@@ -1713,7 +1719,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1782,19 +1788,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="8">
@@ -2015,7 +2008,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="69">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2120,12 +2113,8 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="12" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -2514,7 +2503,7 @@
         <v>22</v>
       </c>
       <c r="C8" s="22" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="23" t="s">
         <v>27</v>
@@ -2525,7 +2514,7 @@
       <c r="F8" s="23" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G8" s="24" t="s">
         <v>30</v>
       </c>
       <c r="H8" s="25" t="s">
@@ -2537,7 +2526,7 @@
         <v>22</v>
       </c>
       <c r="C9" s="22" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="23" t="s">
         <v>9</v>
@@ -2556,137 +2545,137 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="27" t="s">
         <v>34</v>
       </c>
-      <c r="C10" s="29" t="n">
-        <v>6</v>
-      </c>
-      <c r="D10" s="30" t="s">
+      <c r="C10" s="28" t="n">
+        <v>7</v>
+      </c>
+      <c r="D10" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="29" t="s">
+      <c r="E10" s="28" t="s">
         <v>35</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="F10" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="30" t="s">
         <v>37</v>
       </c>
-      <c r="H10" s="32" t="s">
+      <c r="H10" s="31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="28" t="s">
+      <c r="B11" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C11" s="29" t="n">
-        <v>7</v>
-      </c>
-      <c r="D11" s="30" t="s">
+      <c r="C11" s="28" t="n">
+        <v>8</v>
+      </c>
+      <c r="D11" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="29" t="s">
+      <c r="E11" s="28" t="s">
         <v>39</v>
       </c>
-      <c r="F11" s="30" t="s">
+      <c r="F11" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="30" t="s">
         <v>41</v>
       </c>
-      <c r="H11" s="32" t="s">
+      <c r="H11" s="31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="28" t="s">
+      <c r="B12" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C12" s="29" t="n">
-        <v>8</v>
-      </c>
-      <c r="D12" s="30" t="s">
+      <c r="C12" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="E12" s="29" t="s">
+      <c r="D12" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="E12" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="F12" s="30" t="s">
+      <c r="F12" s="29" t="s">
         <v>40</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="30" t="s">
         <v>43</v>
       </c>
-      <c r="H12" s="33" t="s">
+      <c r="H12" s="32" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="28" t="s">
+      <c r="B13" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="29" t="n">
+      <c r="C13" s="28" t="n">
+        <v>10</v>
+      </c>
+      <c r="D13" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="F13" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="G13" s="30" t="s">
+        <v>47</v>
+      </c>
+      <c r="H13" s="31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B14" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C14" s="28" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" s="29" t="s">
+        <v>27</v>
+      </c>
+      <c r="E14" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="F14" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="G14" s="30" t="s">
+        <v>50</v>
+      </c>
+      <c r="H14" s="31" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B15" s="27" t="s">
+        <v>38</v>
+      </c>
+      <c r="C15" s="28" t="n">
+        <v>12</v>
+      </c>
+      <c r="D15" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="D13" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="E13" s="29" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="30" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="31" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="32" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="C14" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="D14" s="30" t="s">
-        <v>27</v>
-      </c>
-      <c r="E14" s="29" t="s">
-        <v>48</v>
-      </c>
-      <c r="F14" s="30" t="s">
-        <v>49</v>
-      </c>
-      <c r="G14" s="31" t="s">
-        <v>50</v>
-      </c>
-      <c r="H14" s="32" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="28" t="s">
-        <v>38</v>
-      </c>
-      <c r="C15" s="29" t="n">
-        <v>11</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>9</v>
-      </c>
-      <c r="E15" s="29" t="s">
+      <c r="E15" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="F15" s="30" t="s">
+      <c r="F15" s="29" t="s">
         <v>52</v>
       </c>
-      <c r="G15" s="31" t="s">
+      <c r="G15" s="30" t="s">
         <v>53</v>
       </c>
       <c r="H15" s="20" t="s">
@@ -2694,163 +2683,163 @@
       </c>
     </row>
     <row r="16" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="28" t="s">
+      <c r="B16" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="29" t="n">
-        <v>12</v>
-      </c>
-      <c r="D16" s="30" t="s">
+      <c r="C16" s="28" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="34" t="s">
+      <c r="E16" s="33" t="s">
         <v>55</v>
       </c>
-      <c r="F16" s="30" t="s">
+      <c r="F16" s="29" t="s">
         <v>56</v>
       </c>
-      <c r="G16" s="31" t="s">
+      <c r="G16" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="H16" s="32" t="s">
+      <c r="H16" s="31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="29" t="n">
-        <v>13</v>
-      </c>
-      <c r="D17" s="30" t="s">
+      <c r="C17" s="28" t="n">
+        <v>14</v>
+      </c>
+      <c r="D17" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E17" s="29" t="s">
+      <c r="E17" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="F17" s="30" t="s">
+      <c r="F17" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="30" t="s">
         <v>60</v>
       </c>
-      <c r="H17" s="32" t="s">
+      <c r="H17" s="31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="27" t="s">
         <v>38</v>
       </c>
-      <c r="C18" s="29" t="n">
-        <v>14</v>
-      </c>
-      <c r="D18" s="30" t="s">
+      <c r="C18" s="28" t="n">
+        <v>15</v>
+      </c>
+      <c r="D18" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="E18" s="34" t="s">
+      <c r="E18" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="F18" s="30" t="s">
+      <c r="F18" s="29" t="s">
         <v>62</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="H18" s="32" t="s">
+      <c r="H18" s="31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="35" t="s">
+      <c r="B19" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="C19" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="D19" s="37" t="s">
+      <c r="C19" s="35" t="n">
+        <v>16</v>
+      </c>
+      <c r="D19" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="36" t="s">
+      <c r="E19" s="35" t="s">
         <v>65</v>
       </c>
-      <c r="F19" s="37" t="s">
+      <c r="F19" s="36" t="s">
         <v>66</v>
       </c>
-      <c r="G19" s="38" t="s">
+      <c r="G19" s="37" t="s">
         <v>67</v>
       </c>
-      <c r="H19" s="39" t="s">
+      <c r="H19" s="38" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="35" t="s">
+      <c r="B20" s="34" t="s">
         <v>64</v>
       </c>
-      <c r="C20" s="36" t="n">
-        <v>16</v>
-      </c>
-      <c r="D20" s="37" t="s">
+      <c r="C20" s="35" t="n">
+        <v>17</v>
+      </c>
+      <c r="D20" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="E20" s="36" t="s">
+      <c r="E20" s="35" t="s">
         <v>68</v>
       </c>
-      <c r="F20" s="37" t="s">
+      <c r="F20" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="G20" s="38" t="s">
+      <c r="G20" s="37" t="s">
         <v>70</v>
       </c>
-      <c r="H20" s="39" t="s">
+      <c r="H20" s="38" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="28" t="s">
+      <c r="B21" s="27" t="s">
         <v>71</v>
       </c>
-      <c r="C21" s="29" t="n">
-        <v>17</v>
-      </c>
-      <c r="D21" s="30" t="s">
+      <c r="C21" s="28" t="n">
+        <v>18</v>
+      </c>
+      <c r="D21" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="E21" s="29" t="s">
+      <c r="E21" s="28" t="s">
         <v>72</v>
       </c>
-      <c r="F21" s="30" t="s">
+      <c r="F21" s="29" t="s">
         <v>73</v>
       </c>
-      <c r="G21" s="31" t="s">
+      <c r="G21" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="H21" s="32" t="s">
+      <c r="H21" s="31" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="92.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="35" t="s">
+      <c r="B22" s="34" t="s">
         <v>75</v>
       </c>
-      <c r="C22" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="D22" s="37" t="s">
+      <c r="C22" s="35" t="n">
+        <v>19</v>
+      </c>
+      <c r="D22" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="E22" s="36" t="s">
+      <c r="E22" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="F22" s="37" t="s">
+      <c r="F22" s="36" t="s">
         <v>77</v>
       </c>
-      <c r="G22" s="40" t="s">
+      <c r="G22" s="39" t="s">
         <v>78</v>
       </c>
-      <c r="H22" s="39" t="s">
+      <c r="H22" s="38" t="s">
         <v>26</v>
       </c>
     </row>
@@ -2924,7 +2913,7 @@
       </c>
     </row>
     <row r="4" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="41" t="s">
+      <c r="B4" s="40" t="s">
         <v>79</v>
       </c>
       <c r="C4" s="6" t="n">
@@ -2947,7 +2936,7 @@
       </c>
     </row>
     <row r="5" customFormat="false" ht="90.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="41"/>
+      <c r="B5" s="40"/>
       <c r="C5" s="11" t="n">
         <v>2</v>
       </c>
@@ -2968,235 +2957,235 @@
       </c>
     </row>
     <row r="6" customFormat="false" ht="60.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="41"/>
+      <c r="B6" s="40"/>
       <c r="C6" s="20" t="n">
         <v>3</v>
       </c>
       <c r="D6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="42" t="s">
+      <c r="E6" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="F6" s="43" t="s">
+      <c r="F6" s="42" t="s">
         <v>89</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="H6" s="42" t="s">
+      <c r="H6" s="41" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="105.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="44" t="s">
+      <c r="B7" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="C7" s="45" t="n">
+      <c r="C7" s="44" t="n">
         <v>4</v>
       </c>
-      <c r="D7" s="46" t="s">
+      <c r="D7" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="47" t="s">
+      <c r="E7" s="46" t="s">
         <v>93</v>
       </c>
-      <c r="F7" s="46" t="s">
+      <c r="F7" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="G7" s="47" t="s">
+      <c r="G7" s="46" t="s">
         <v>95</v>
       </c>
-      <c r="H7" s="48" t="s">
+      <c r="H7" s="47" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="105.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="44"/>
-      <c r="C8" s="49" t="n">
+      <c r="B8" s="43"/>
+      <c r="C8" s="48" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="46" t="s">
+      <c r="D8" s="45" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="49" t="s">
         <v>97</v>
       </c>
-      <c r="F8" s="51" t="s">
+      <c r="F8" s="50" t="s">
         <v>98</v>
       </c>
-      <c r="G8" s="50" t="s">
+      <c r="G8" s="49" t="s">
         <v>99</v>
       </c>
-      <c r="H8" s="48"/>
+      <c r="H8" s="47"/>
     </row>
     <row r="9" customFormat="false" ht="75.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="44"/>
-      <c r="C9" s="52" t="n">
+      <c r="B9" s="43"/>
+      <c r="C9" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="D9" s="53" t="s">
+      <c r="D9" s="52" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="54" t="s">
+      <c r="E9" s="53" t="s">
         <v>100</v>
       </c>
-      <c r="F9" s="55" t="s">
+      <c r="F9" s="54" t="s">
         <v>89</v>
       </c>
-      <c r="G9" s="54" t="s">
+      <c r="G9" s="53" t="s">
         <v>101</v>
       </c>
-      <c r="H9" s="48"/>
+      <c r="H9" s="47"/>
     </row>
     <row r="10" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="56" t="s">
+      <c r="B10" s="55" t="s">
         <v>102</v>
       </c>
-      <c r="C10" s="57" t="n">
+      <c r="C10" s="56" t="n">
         <v>11</v>
       </c>
-      <c r="D10" s="58" t="s">
+      <c r="D10" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="59" t="s">
+      <c r="E10" s="58" t="s">
         <v>103</v>
       </c>
-      <c r="F10" s="58" t="s">
+      <c r="F10" s="57" t="s">
         <v>104</v>
       </c>
-      <c r="G10" s="60" t="s">
+      <c r="G10" s="59" t="s">
         <v>105</v>
       </c>
-      <c r="H10" s="59" t="s">
+      <c r="H10" s="58" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="60.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="56"/>
-      <c r="C11" s="61" t="n">
+      <c r="B11" s="55"/>
+      <c r="C11" s="60" t="n">
         <v>12</v>
       </c>
-      <c r="D11" s="62" t="s">
+      <c r="D11" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="63" t="s">
+      <c r="E11" s="62" t="s">
         <v>107</v>
       </c>
-      <c r="F11" s="64" t="s">
+      <c r="F11" s="63" t="s">
         <v>104</v>
       </c>
-      <c r="G11" s="65" t="s">
+      <c r="G11" s="64" t="s">
         <v>108</v>
       </c>
-      <c r="H11" s="66" t="s">
+      <c r="H11" s="65" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="60.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="43" t="s">
         <v>110</v>
       </c>
-      <c r="C12" s="45" t="n">
+      <c r="C12" s="44" t="n">
         <v>23</v>
       </c>
-      <c r="D12" s="46" t="s">
+      <c r="D12" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="47" t="s">
+      <c r="E12" s="46" t="s">
         <v>111</v>
       </c>
-      <c r="F12" s="46" t="s">
+      <c r="F12" s="45" t="s">
         <v>112</v>
       </c>
-      <c r="G12" s="47" t="s">
+      <c r="G12" s="46" t="s">
         <v>113</v>
       </c>
-      <c r="H12" s="67" t="s">
+      <c r="H12" s="66" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="60.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="44"/>
-      <c r="C13" s="49" t="n">
+      <c r="B13" s="43"/>
+      <c r="C13" s="48" t="n">
         <v>24</v>
       </c>
-      <c r="D13" s="46" t="s">
+      <c r="D13" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="50" t="s">
+      <c r="E13" s="49" t="s">
         <v>114</v>
       </c>
-      <c r="F13" s="51" t="s">
+      <c r="F13" s="50" t="s">
         <v>115</v>
       </c>
-      <c r="G13" s="50" t="s">
+      <c r="G13" s="49" t="s">
         <v>116</v>
       </c>
-      <c r="H13" s="68" t="s">
+      <c r="H13" s="67" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="60.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="44"/>
-      <c r="C14" s="49" t="n">
+      <c r="B14" s="43"/>
+      <c r="C14" s="48" t="n">
         <v>25</v>
       </c>
-      <c r="D14" s="46" t="s">
+      <c r="D14" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="E14" s="50" t="s">
+      <c r="E14" s="49" t="s">
         <v>117</v>
       </c>
-      <c r="F14" s="51" t="s">
+      <c r="F14" s="50" t="s">
         <v>118</v>
       </c>
-      <c r="G14" s="50" t="s">
+      <c r="G14" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="H14" s="68" t="s">
+      <c r="H14" s="67" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="60.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="44"/>
-      <c r="C15" s="49" t="n">
+      <c r="B15" s="43"/>
+      <c r="C15" s="48" t="n">
         <v>26</v>
       </c>
-      <c r="D15" s="46" t="s">
+      <c r="D15" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="50" t="s">
+      <c r="E15" s="49" t="s">
         <v>120</v>
       </c>
-      <c r="F15" s="51" t="s">
+      <c r="F15" s="50" t="s">
         <v>121</v>
       </c>
-      <c r="G15" s="50" t="s">
+      <c r="G15" s="49" t="s">
         <v>122</v>
       </c>
-      <c r="H15" s="68" t="s">
+      <c r="H15" s="67" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="60.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="44"/>
-      <c r="C16" s="52" t="n">
+      <c r="B16" s="43"/>
+      <c r="C16" s="51" t="n">
         <v>27</v>
       </c>
-      <c r="D16" s="46" t="s">
+      <c r="D16" s="45" t="s">
         <v>27</v>
       </c>
-      <c r="E16" s="54" t="s">
+      <c r="E16" s="53" t="s">
         <v>123</v>
       </c>
-      <c r="F16" s="55" t="s">
+      <c r="F16" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="54" t="s">
+      <c r="G16" s="53" t="s">
         <v>125</v>
       </c>
-      <c r="H16" s="69" t="s">
+      <c r="H16" s="68" t="s">
         <v>26</v>
       </c>
     </row>
